--- a/plans/待做产品项目清单.xlsx
+++ b/plans/待做产品项目清单.xlsx
@@ -5206,7 +5206,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>✓ 可作作品集案例（案例②）</t>
+          <t>✓ 可作作品集案例（案例①）</t>
         </is>
       </c>
     </row>
@@ -5447,6 +5447,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="C10" s="12" t="inlineStr">
         <is>
